--- a/AAII_Financials/Quarterly/PGID_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PGID_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="92">
   <si>
     <t>PGID</t>
   </si>
@@ -656,140 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43769</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -818,28 +822,28 @@
         <v>0</v>
       </c>
       <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3">
         <v>400</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -880,8 +884,11 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -909,8 +916,8 @@
       <c r="K9" s="3">
         <v>0</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>4</v>
+      <c r="L9" s="3">
+        <v>0</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>4</v>
@@ -972,8 +979,11 @@
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1001,8 +1011,8 @@
       <c r="K10" s="3">
         <v>0</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
+      <c r="L10" s="3">
+        <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
@@ -1064,8 +1074,11 @@
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1299,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1291,19 +1311,19 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
@@ -1311,12 +1331,12 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1332,8 +1352,8 @@
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1374,8 +1394,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1385,14 +1408,14 @@
       <c r="E15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
+      <c r="F15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -1403,8 +1426,8 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>4</v>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>4</v>
@@ -1424,8 +1447,8 @@
       <c r="R15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,8 +1523,9 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1506,19 +1533,19 @@
         <v>100</v>
       </c>
       <c r="E17" s="3">
+        <v>100</v>
+      </c>
+      <c r="F17" s="3">
         <v>200</v>
       </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
       <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
         <v>100</v>
       </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
       <c r="I17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3">
         <v>100</v>
@@ -1527,11 +1554,11 @@
         <v>100</v>
       </c>
       <c r="L17" s="3">
+        <v>100</v>
+      </c>
+      <c r="M17" s="3">
         <v>200</v>
       </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
       <c r="N17" s="3">
         <v>0</v>
       </c>
@@ -1539,11 +1566,11 @@
         <v>0</v>
       </c>
       <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
         <v>900</v>
       </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
       <c r="R17" s="3">
         <v>0</v>
       </c>
@@ -1589,8 +1616,11 @@
       <c r="AF17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1598,19 +1628,19 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-200</v>
       </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
       <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
         <v>-100</v>
       </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
       <c r="I18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3">
         <v>-100</v>
@@ -1621,8 +1651,8 @@
       <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
+      <c r="M18" s="3">
+        <v>-100</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>4</v>
@@ -1630,17 +1660,17 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-500</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T18" s="3">
         <v>0</v>
@@ -1681,8 +1711,11 @@
       <c r="AF18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1748,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1742,13 +1776,13 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>4</v>
@@ -1756,17 +1790,17 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
@@ -1807,8 +1841,11 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1816,29 +1853,29 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>-200</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
       <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <v>-100</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
       <c r="I21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
         <v>-100</v>
       </c>
       <c r="K21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L21" s="3">
         <v>200</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1899,8 +1936,11 @@
       <c r="AF21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1955,14 +1995,14 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>4</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -1991,41 +2031,44 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>-200</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
       <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>-100</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3">
         <v>-100</v>
       </c>
       <c r="K23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L23" s="3">
         <v>100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-100</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
       <c r="N23" s="3">
         <v>0</v>
       </c>
@@ -2033,11 +2076,11 @@
         <v>0</v>
       </c>
       <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-800</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
         <v>0</v>
       </c>
@@ -2083,8 +2126,11 @@
       <c r="AF23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2175,8 +2221,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,41 +2316,44 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>-200</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
       <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>-100</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
       <c r="I26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J26" s="3">
         <v>-100</v>
       </c>
       <c r="K26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L26" s="3">
         <v>100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-100</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
       <c r="N26" s="3">
         <v>0</v>
       </c>
@@ -2309,11 +2361,11 @@
         <v>0</v>
       </c>
       <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-800</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
         <v>0</v>
       </c>
@@ -2359,41 +2411,44 @@
       <c r="AF26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>-200</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
       <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>-100</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
       <c r="I27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3">
         <v>-100</v>
       </c>
       <c r="K27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L27" s="3">
         <v>100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-100</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
       <c r="N27" s="3">
         <v>0</v>
       </c>
@@ -2401,11 +2456,11 @@
         <v>0</v>
       </c>
       <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-800</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
         <v>0</v>
       </c>
@@ -2451,8 +2506,11 @@
       <c r="AF27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2886,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2846,13 +2916,13 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>4</v>
@@ -2860,17 +2930,17 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T32" s="3">
         <v>0</v>
@@ -2911,41 +2981,44 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>-200</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
       <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>-100</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
       <c r="I33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3">
         <v>-100</v>
       </c>
       <c r="K33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L33" s="3">
         <v>100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-100</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
       <c r="N33" s="3">
         <v>0</v>
       </c>
@@ -2953,11 +3026,11 @@
         <v>0</v>
       </c>
       <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-800</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
         <v>0</v>
       </c>
@@ -3003,8 +3076,11 @@
       <c r="AF33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,41 +3171,44 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>-200</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
       <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>-100</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
       <c r="I35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3">
         <v>-100</v>
       </c>
       <c r="K35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L35" s="3">
         <v>100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-100</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
       <c r="N35" s="3">
         <v>0</v>
       </c>
@@ -3137,11 +3216,11 @@
         <v>0</v>
       </c>
       <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-800</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
         <v>0</v>
       </c>
@@ -3187,105 +3266,111 @@
       <c r="AF35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43769</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,8 +3438,9 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3364,29 +3451,29 @@
         <v>400</v>
       </c>
       <c r="F41" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G41" s="3">
         <v>500</v>
       </c>
       <c r="H41" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I41" s="3">
         <v>600</v>
       </c>
       <c r="J41" s="3">
+        <v>600</v>
+      </c>
+      <c r="K41" s="3">
         <v>500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>100</v>
       </c>
-      <c r="M41" s="3">
-        <v>0</v>
-      </c>
       <c r="N41" s="3">
         <v>0</v>
       </c>
@@ -3423,11 +3510,11 @@
       <c r="Y41" s="3">
         <v>0</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>0</v>
+      <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB41" s="3">
         <v>0</v>
@@ -3444,8 +3531,11 @@
       <c r="AF41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,8 +3626,11 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3568,8 +3661,8 @@
       <c r="L43" s="3">
         <v>0</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
+      <c r="M43" s="3">
+        <v>0</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
@@ -3586,8 +3679,8 @@
       <c r="R43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -3628,8 +3721,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3640,13 +3736,13 @@
         <v>600</v>
       </c>
       <c r="F44" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="G44" s="3">
         <v>700</v>
       </c>
       <c r="H44" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="I44" s="3">
         <v>800</v>
@@ -3660,8 +3756,8 @@
       <c r="L44" s="3">
         <v>800</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>4</v>
+      <c r="M44" s="3">
+        <v>800</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>4</v>
@@ -3678,8 +3774,8 @@
       <c r="R44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
@@ -3720,8 +3816,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3752,8 +3851,8 @@
       <c r="L45" s="3">
         <v>0</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>4</v>
+      <c r="M45" s="3">
+        <v>0</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>4</v>
@@ -3770,8 +3869,8 @@
       <c r="R45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S45" s="3">
-        <v>0</v>
+      <c r="S45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T45" s="3">
         <v>0</v>
@@ -3788,14 +3887,14 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="3" t="s">
-        <v>4</v>
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>0</v>
       </c>
       <c r="AB45" s="3" t="s">
         <v>4</v>
@@ -3812,8 +3911,11 @@
       <c r="AF45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3821,32 +3923,32 @@
         <v>1000</v>
       </c>
       <c r="E46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F46" s="3">
         <v>1100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1300</v>
-      </c>
-      <c r="H46" s="3">
-        <v>1400</v>
       </c>
       <c r="I46" s="3">
         <v>1400</v>
       </c>
       <c r="J46" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K46" s="3">
         <v>1300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>900</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -3904,8 +4006,11 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,8 +4101,11 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4026,11 +4134,11 @@
         <v>0</v>
       </c>
       <c r="L48" s="3">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3">
         <v>500</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4046,8 +4154,8 @@
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
@@ -4088,8 +4196,11 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4115,13 +4226,13 @@
         <v>300</v>
       </c>
       <c r="K49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L49" s="3">
         <v>200</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>4</v>
+      <c r="M49" s="3">
+        <v>200</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>4</v>
@@ -4138,8 +4249,8 @@
       <c r="R49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4481,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4381,11 +4501,11 @@
       <c r="G52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>4</v>
@@ -4408,8 +4528,8 @@
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -4456,8 +4576,11 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,41 +4671,44 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="E54" s="3">
         <v>1300</v>
       </c>
       <c r="F54" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G54" s="3">
         <v>1500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1600</v>
-      </c>
-      <c r="H54" s="3">
-        <v>1700</v>
       </c>
       <c r="I54" s="3">
         <v>1700</v>
       </c>
       <c r="J54" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K54" s="3">
         <v>1600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1700</v>
       </c>
-      <c r="M54" s="3">
-        <v>0</v>
-      </c>
       <c r="N54" s="3">
         <v>0</v>
       </c>
@@ -4640,8 +4766,11 @@
       <c r="AF54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,8 +4838,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4740,8 +4871,8 @@
       <c r="L57" s="3">
         <v>0</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
+      <c r="M57" s="3">
+        <v>0</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>4</v>
@@ -4758,8 +4889,8 @@
       <c r="R57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
+      <c r="S57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T57" s="3">
         <v>0</v>
@@ -4800,16 +4931,19 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
         <v>0</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>4</v>
+      <c r="E58" s="3">
+        <v>0</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>4</v>
@@ -4817,8 +4951,8 @@
       <c r="G58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
+      <c r="H58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -4827,7 +4961,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L58" s="3">
         <v>100</v>
@@ -4848,7 +4982,7 @@
         <v>100</v>
       </c>
       <c r="R58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -4878,13 +5012,13 @@
         <v>0</v>
       </c>
       <c r="AB58" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AC58" s="3">
         <v>400</v>
       </c>
       <c r="AD58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AE58" s="3">
         <v>300</v>
@@ -4892,8 +5026,11 @@
       <c r="AF58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4915,17 +5052,17 @@
       <c r="I59" s="3">
         <v>0</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
+      <c r="J59" s="3">
+        <v>0</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
+        <v>0</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>4</v>
@@ -4933,8 +5070,8 @@
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
+      <c r="P59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q59" s="3">
         <v>0</v>
@@ -4970,7 +5107,7 @@
         <v>0</v>
       </c>
       <c r="AB59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC59" s="3">
         <v>100</v>
@@ -4984,8 +5121,11 @@
       <c r="AF59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5011,7 +5151,7 @@
         <v>0</v>
       </c>
       <c r="K60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L60" s="3">
         <v>100</v>
@@ -5032,7 +5172,7 @@
         <v>100</v>
       </c>
       <c r="R60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S60" s="3">
         <v>0</v>
@@ -5062,7 +5202,7 @@
         <v>0</v>
       </c>
       <c r="AB60" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AC60" s="3">
         <v>400</v>
@@ -5076,8 +5216,11 @@
       <c r="AF60" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5100,7 +5243,7 @@
         <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5168,19 +5311,22 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G62" s="3">
         <v>0</v>
@@ -5191,17 +5337,17 @@
       <c r="I62" s="3">
         <v>0</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
+      <c r="M62" s="3">
+        <v>0</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>4</v>
@@ -5218,8 +5364,8 @@
       <c r="R62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,8 +5691,11 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5551,7 +5709,7 @@
         <v>100</v>
       </c>
       <c r="G66" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H66" s="3">
         <v>200</v>
@@ -5560,10 +5718,10 @@
         <v>200</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L66" s="3">
         <v>100</v>
@@ -5584,7 +5742,7 @@
         <v>100</v>
       </c>
       <c r="R66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S66" s="3">
         <v>0</v>
@@ -5614,7 +5772,7 @@
         <v>0</v>
       </c>
       <c r="AB66" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AC66" s="3">
         <v>400</v>
@@ -5628,8 +5786,11 @@
       <c r="AF66" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,40 +6201,43 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-4800</v>
+        <v>-4900</v>
       </c>
       <c r="E72" s="3">
         <v>-4800</v>
       </c>
       <c r="F72" s="3">
-        <v>-4600</v>
+        <v>-4800</v>
       </c>
       <c r="G72" s="3">
         <v>-4600</v>
       </c>
       <c r="H72" s="3">
-        <v>-4400</v>
+        <v>-4600</v>
       </c>
       <c r="I72" s="3">
         <v>-4400</v>
       </c>
       <c r="J72" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="K72" s="3">
         <v>-4300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-4200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-4300</v>
-      </c>
-      <c r="M72" s="3">
-        <v>-700</v>
       </c>
       <c r="N72" s="3">
         <v>-700</v>
@@ -6078,7 +6252,7 @@
         <v>-700</v>
       </c>
       <c r="R72" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="S72" s="3">
         <v>-600</v>
@@ -6122,8 +6296,11 @@
       <c r="AF72" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,40 +6581,43 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="E76" s="3">
         <v>1200</v>
       </c>
       <c r="F76" s="3">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="G76" s="3">
         <v>1400</v>
       </c>
       <c r="H76" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="I76" s="3">
         <v>1500</v>
       </c>
       <c r="J76" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K76" s="3">
         <v>1600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1600</v>
-      </c>
-      <c r="M76" s="3">
-        <v>-100</v>
       </c>
       <c r="N76" s="3">
         <v>-100</v>
@@ -6443,7 +6629,7 @@
         <v>-100</v>
       </c>
       <c r="Q76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R76" s="3">
         <v>0</v>
@@ -6476,7 +6662,7 @@
         <v>0</v>
       </c>
       <c r="AB76" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="AC76" s="3">
         <v>-400</v>
@@ -6490,8 +6676,11 @@
       <c r="AF76" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,138 +6771,144 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43769</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>-200</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
       <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>-100</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
       <c r="I81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J81" s="3">
         <v>-100</v>
       </c>
       <c r="K81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L81" s="3">
         <v>100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-100</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
       <c r="N81" s="3">
         <v>0</v>
       </c>
@@ -6721,11 +6916,11 @@
         <v>0</v>
       </c>
       <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-800</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
         <v>0</v>
       </c>
@@ -6771,8 +6966,11 @@
       <c r="AF81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7003,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6834,8 +7033,8 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>4</v>
@@ -6852,8 +7051,8 @@
       <c r="Q83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="R83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -6897,8 +7096,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,41 +7571,44 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E89" s="3">
         <v>0</v>
       </c>
       <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
       <c r="H89" s="3">
         <v>0</v>
       </c>
       <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>500</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
       <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
       <c r="N89" s="3">
         <v>0</v>
       </c>
@@ -7449,8 +7666,11 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7703,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7575,8 +7796,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,8 +7986,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7777,19 +8007,19 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>600</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>4</v>
@@ -7806,8 +8036,8 @@
       <c r="Q94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
@@ -7851,8 +8081,11 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,8 +8496,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8271,23 +8517,23 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I100" s="3">
         <v>100</v>
       </c>
       <c r="J100" s="3">
+        <v>100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
@@ -8295,25 +8541,25 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>4</v>
+      <c r="T100" s="3">
+        <v>0</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
+      <c r="V100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
@@ -8345,8 +8591,11 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,23 +8686,26 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
@@ -8461,11 +8713,11 @@
         <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>500</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
@@ -8527,6 +8779,9 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PGID_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PGID_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
   <si>
     <t>PGID</t>
   </si>
@@ -656,144 +656,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
         <v>45230</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43951</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -825,28 +829,28 @@
         <v>0</v>
       </c>
       <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
         <v>100</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3">
         <v>400</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
+      <c r="T8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
@@ -887,8 +891,11 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -919,8 +926,8 @@
       <c r="L9" s="3">
         <v>0</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
+      <c r="M9" s="3">
+        <v>0</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>4</v>
@@ -982,8 +989,11 @@
       <c r="AG9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1014,8 +1024,8 @@
       <c r="L10" s="3">
         <v>0</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
+      <c r="M10" s="3">
+        <v>0</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
@@ -1077,8 +1087,11 @@
       <c r="AG10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,8 +1125,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1207,8 +1221,11 @@
       <c r="AG12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1319,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1314,19 +1334,19 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
@@ -1334,12 +1354,12 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1355,8 +1375,8 @@
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1397,13 +1417,16 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>4</v>
+      <c r="D15" s="3">
+        <v>0</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>4</v>
@@ -1411,14 +1434,14 @@
       <c r="F15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
+      <c r="G15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1429,8 +1452,8 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>4</v>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>4</v>
@@ -1450,8 +1473,8 @@
       <c r="S15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="T15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1492,8 +1515,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,31 +1550,32 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E17" s="3">
         <v>100</v>
       </c>
       <c r="F17" s="3">
+        <v>100</v>
+      </c>
+      <c r="G17" s="3">
         <v>200</v>
       </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
       <c r="H17" s="3">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
         <v>100</v>
       </c>
-      <c r="I17" s="3">
-        <v>0</v>
-      </c>
       <c r="J17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3">
         <v>100</v>
@@ -1557,11 +1584,11 @@
         <v>100</v>
       </c>
       <c r="M17" s="3">
+        <v>100</v>
+      </c>
+      <c r="N17" s="3">
         <v>200</v>
       </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
       <c r="O17" s="3">
         <v>0</v>
       </c>
@@ -1569,11 +1596,11 @@
         <v>0</v>
       </c>
       <c r="Q17" s="3">
+        <v>0</v>
+      </c>
+      <c r="R17" s="3">
         <v>900</v>
       </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
       <c r="S17" s="3">
         <v>0</v>
       </c>
@@ -1619,8 +1646,11 @@
       <c r="AG17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1631,19 +1661,19 @@
         <v>-100</v>
       </c>
       <c r="F18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G18" s="3">
         <v>-200</v>
       </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
       <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
         <v>-100</v>
       </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
       <c r="J18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3">
         <v>-100</v>
@@ -1654,8 +1684,8 @@
       <c r="M18" s="3">
         <v>-100</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>4</v>
+      <c r="N18" s="3">
+        <v>-100</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>4</v>
@@ -1663,17 +1693,17 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3">
         <v>-500</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
+      <c r="T18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U18" s="3">
         <v>0</v>
@@ -1714,8 +1744,11 @@
       <c r="AG18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,8 +1782,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1779,13 +1813,13 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>4</v>
@@ -1793,17 +1827,17 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
+      <c r="T20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U20" s="3">
         <v>0</v>
@@ -1844,8 +1878,11 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1853,32 +1890,32 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
         <v>-200</v>
       </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>-100</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>-100</v>
       </c>
       <c r="L21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M21" s="3">
         <v>200</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1939,8 +1976,11 @@
       <c r="AG21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1998,14 +2038,14 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>4</v>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -2034,44 +2074,47 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
         <v>-100</v>
       </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
       <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
         <v>-200</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
         <v>-100</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3">
         <v>-100</v>
       </c>
       <c r="L23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M23" s="3">
         <v>100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-100</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
       <c r="O23" s="3">
         <v>0</v>
       </c>
@@ -2079,11 +2122,11 @@
         <v>0</v>
       </c>
       <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
         <v>-800</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
       <c r="S23" s="3">
         <v>0</v>
       </c>
@@ -2129,8 +2172,11 @@
       <c r="AG23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2224,8 +2270,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,44 +2368,47 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
         <v>-100</v>
       </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
       <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
         <v>-200</v>
       </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
       <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
         <v>-100</v>
       </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
       <c r="J26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3">
         <v>-100</v>
       </c>
       <c r="L26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M26" s="3">
         <v>100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-100</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
       <c r="O26" s="3">
         <v>0</v>
       </c>
@@ -2364,11 +2416,11 @@
         <v>0</v>
       </c>
       <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
         <v>-800</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
       <c r="S26" s="3">
         <v>0</v>
       </c>
@@ -2414,44 +2466,47 @@
       <c r="AG26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
         <v>-100</v>
       </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
       <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
         <v>-200</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
       <c r="J27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K27" s="3">
         <v>-100</v>
       </c>
       <c r="L27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M27" s="3">
         <v>100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-100</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
       <c r="O27" s="3">
         <v>0</v>
       </c>
@@ -2459,11 +2514,11 @@
         <v>0</v>
       </c>
       <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
         <v>-800</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
       <c r="S27" s="3">
         <v>0</v>
       </c>
@@ -2509,8 +2564,11 @@
       <c r="AG27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,8 +2956,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2919,13 +2989,13 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>4</v>
@@ -2933,17 +3003,17 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
+      <c r="T32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U32" s="3">
         <v>0</v>
@@ -2984,44 +3054,47 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
         <v>-100</v>
       </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
       <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
         <v>-200</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>-100</v>
       </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
       <c r="J33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K33" s="3">
         <v>-100</v>
       </c>
       <c r="L33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M33" s="3">
         <v>100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-100</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
       <c r="O33" s="3">
         <v>0</v>
       </c>
@@ -3029,11 +3102,11 @@
         <v>0</v>
       </c>
       <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>-800</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
         <v>0</v>
       </c>
@@ -3079,8 +3152,11 @@
       <c r="AG33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,44 +3250,47 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
         <v>-100</v>
       </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
       <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
         <v>-200</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>-100</v>
       </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
       <c r="J35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K35" s="3">
         <v>-100</v>
       </c>
       <c r="L35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M35" s="3">
         <v>100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-100</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
       <c r="O35" s="3">
         <v>0</v>
       </c>
@@ -3219,11 +3298,11 @@
         <v>0</v>
       </c>
       <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>-800</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
         <v>0</v>
       </c>
@@ -3269,108 +3348,114 @@
       <c r="AG35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
         <v>45230</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43951</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,13 +3525,14 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E41" s="3">
         <v>400</v>
@@ -3454,29 +3541,29 @@
         <v>400</v>
       </c>
       <c r="G41" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H41" s="3">
         <v>500</v>
       </c>
       <c r="I41" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J41" s="3">
         <v>600</v>
       </c>
       <c r="K41" s="3">
+        <v>600</v>
+      </c>
+      <c r="L41" s="3">
         <v>500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>100</v>
       </c>
-      <c r="N41" s="3">
-        <v>0</v>
-      </c>
       <c r="O41" s="3">
         <v>0</v>
       </c>
@@ -3513,11 +3600,11 @@
       <c r="Z41" s="3">
         <v>0</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB41" s="3">
-        <v>0</v>
+      <c r="AA41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC41" s="3">
         <v>0</v>
@@ -3534,8 +3621,11 @@
       <c r="AG41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3629,8 +3719,11 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3664,8 +3757,8 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
+      <c r="N43" s="3">
+        <v>0</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>4</v>
@@ -3682,8 +3775,8 @@
       <c r="S43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="T43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -3724,8 +3817,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3739,13 +3835,13 @@
         <v>600</v>
       </c>
       <c r="G44" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="H44" s="3">
         <v>700</v>
       </c>
       <c r="I44" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="J44" s="3">
         <v>800</v>
@@ -3759,8 +3855,8 @@
       <c r="M44" s="3">
         <v>800</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
+      <c r="N44" s="3">
+        <v>800</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>4</v>
@@ -3777,8 +3873,8 @@
       <c r="S44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
+      <c r="T44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
@@ -3819,8 +3915,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3854,8 +3953,8 @@
       <c r="M45" s="3">
         <v>0</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
+      <c r="N45" s="3">
+        <v>0</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>4</v>
@@ -3872,8 +3971,8 @@
       <c r="S45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
+      <c r="T45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U45" s="3">
         <v>0</v>
@@ -3890,14 +3989,14 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>4</v>
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>0</v>
       </c>
       <c r="AC45" s="3" t="s">
         <v>4</v>
@@ -3914,44 +4013,47 @@
       <c r="AG45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E46" s="3">
         <v>1000</v>
       </c>
       <c r="F46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G46" s="3">
         <v>1100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1300</v>
-      </c>
-      <c r="I46" s="3">
-        <v>1400</v>
       </c>
       <c r="J46" s="3">
         <v>1400</v>
       </c>
       <c r="K46" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L46" s="3">
         <v>1300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>900</v>
       </c>
-      <c r="N46" s="3">
-        <v>0</v>
-      </c>
       <c r="O46" s="3">
         <v>0</v>
       </c>
@@ -4009,8 +4111,11 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4104,8 +4209,11 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4137,11 +4245,11 @@
         <v>0</v>
       </c>
       <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3">
         <v>500</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4157,8 +4265,8 @@
       <c r="S48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -4199,8 +4307,11 @@
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4229,13 +4340,13 @@
         <v>300</v>
       </c>
       <c r="L49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M49" s="3">
         <v>200</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>4</v>
+      <c r="N49" s="3">
+        <v>200</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>4</v>
@@ -4252,8 +4363,8 @@
       <c r="S49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -4294,8 +4405,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,8 +4601,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4504,11 +4624,11 @@
       <c r="H52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
@@ -4531,8 +4651,8 @@
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -4579,8 +4699,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,8 +4797,11 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4683,35 +4809,35 @@
         <v>1200</v>
       </c>
       <c r="E54" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F54" s="3">
         <v>1300</v>
       </c>
       <c r="G54" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H54" s="3">
         <v>1500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1600</v>
-      </c>
-      <c r="I54" s="3">
-        <v>1700</v>
       </c>
       <c r="J54" s="3">
         <v>1700</v>
       </c>
       <c r="K54" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L54" s="3">
         <v>1600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1700</v>
       </c>
-      <c r="N54" s="3">
-        <v>0</v>
-      </c>
       <c r="O54" s="3">
         <v>0</v>
       </c>
@@ -4769,8 +4895,11 @@
       <c r="AG54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,8 +4969,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4874,8 +5005,8 @@
       <c r="M57" s="3">
         <v>0</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
+      <c r="N57" s="3">
+        <v>0</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>4</v>
@@ -4892,8 +5023,8 @@
       <c r="S57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
+      <c r="T57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
@@ -4934,8 +5065,11 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4945,8 +5079,8 @@
       <c r="E58" s="3">
         <v>0</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
+      <c r="F58" s="3">
+        <v>0</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>4</v>
@@ -4954,8 +5088,8 @@
       <c r="H58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
+      <c r="I58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -4964,7 +5098,7 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M58" s="3">
         <v>100</v>
@@ -4985,7 +5119,7 @@
         <v>100</v>
       </c>
       <c r="S58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -5015,13 +5149,13 @@
         <v>0</v>
       </c>
       <c r="AC58" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AD58" s="3">
         <v>400</v>
       </c>
       <c r="AE58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AF58" s="3">
         <v>300</v>
@@ -5029,8 +5163,11 @@
       <c r="AG58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5055,17 +5192,17 @@
       <c r="J59" s="3">
         <v>0</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
+      <c r="K59" s="3">
+        <v>0</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
+        <v>0</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>4</v>
@@ -5073,8 +5210,8 @@
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R59" s="3">
         <v>0</v>
@@ -5110,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="AC59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD59" s="3">
         <v>100</v>
@@ -5124,8 +5261,11 @@
       <c r="AG59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5154,7 +5294,7 @@
         <v>0</v>
       </c>
       <c r="L60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M60" s="3">
         <v>100</v>
@@ -5175,7 +5315,7 @@
         <v>100</v>
       </c>
       <c r="S60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T60" s="3">
         <v>0</v>
@@ -5205,7 +5345,7 @@
         <v>0</v>
       </c>
       <c r="AC60" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AD60" s="3">
         <v>400</v>
@@ -5219,8 +5359,11 @@
       <c r="AG60" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5246,7 +5389,7 @@
         <v>100</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -5314,22 +5457,25 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
+      <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H62" s="3">
         <v>0</v>
@@ -5340,17 +5486,17 @@
       <c r="J62" s="3">
         <v>0</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
+      <c r="N62" s="3">
+        <v>0</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>4</v>
@@ -5367,8 +5513,8 @@
       <c r="S62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="T62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
@@ -5409,8 +5555,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,8 +5849,11 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5712,7 +5870,7 @@
         <v>100</v>
       </c>
       <c r="H66" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I66" s="3">
         <v>200</v>
@@ -5721,10 +5879,10 @@
         <v>200</v>
       </c>
       <c r="K66" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M66" s="3">
         <v>100</v>
@@ -5745,7 +5903,7 @@
         <v>100</v>
       </c>
       <c r="S66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T66" s="3">
         <v>0</v>
@@ -5775,7 +5933,7 @@
         <v>0</v>
       </c>
       <c r="AC66" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AD66" s="3">
         <v>400</v>
@@ -5789,8 +5947,11 @@
       <c r="AG66" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,8 +6375,11 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6213,34 +6387,34 @@
         <v>-4900</v>
       </c>
       <c r="E72" s="3">
-        <v>-4800</v>
+        <v>-4900</v>
       </c>
       <c r="F72" s="3">
         <v>-4800</v>
       </c>
       <c r="G72" s="3">
-        <v>-4600</v>
+        <v>-4800</v>
       </c>
       <c r="H72" s="3">
         <v>-4600</v>
       </c>
       <c r="I72" s="3">
-        <v>-4400</v>
+        <v>-4600</v>
       </c>
       <c r="J72" s="3">
         <v>-4400</v>
       </c>
       <c r="K72" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="L72" s="3">
         <v>-4300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-4200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-4300</v>
-      </c>
-      <c r="N72" s="3">
-        <v>-700</v>
       </c>
       <c r="O72" s="3">
         <v>-700</v>
@@ -6255,7 +6429,7 @@
         <v>-700</v>
       </c>
       <c r="S72" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="T72" s="3">
         <v>-600</v>
@@ -6299,8 +6473,11 @@
       <c r="AG72" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,8 +6767,11 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6593,34 +6779,34 @@
         <v>1100</v>
       </c>
       <c r="E76" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="F76" s="3">
         <v>1200</v>
       </c>
       <c r="G76" s="3">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="H76" s="3">
         <v>1400</v>
       </c>
       <c r="I76" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="J76" s="3">
         <v>1500</v>
       </c>
       <c r="K76" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L76" s="3">
         <v>1600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1600</v>
-      </c>
-      <c r="N76" s="3">
-        <v>-100</v>
       </c>
       <c r="O76" s="3">
         <v>-100</v>
@@ -6632,7 +6818,7 @@
         <v>-100</v>
       </c>
       <c r="R76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S76" s="3">
         <v>0</v>
@@ -6665,7 +6851,7 @@
         <v>0</v>
       </c>
       <c r="AC76" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="AD76" s="3">
         <v>-400</v>
@@ -6679,8 +6865,11 @@
       <c r="AG76" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,144 +6963,150 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
         <v>45230</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43951</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3">
         <v>-100</v>
       </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
       <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
         <v>-200</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
         <v>-100</v>
       </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
       <c r="J81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K81" s="3">
         <v>-100</v>
       </c>
       <c r="L81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M81" s="3">
         <v>100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-100</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
       <c r="O81" s="3">
         <v>0</v>
       </c>
@@ -6919,11 +7114,11 @@
         <v>0</v>
       </c>
       <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>-800</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
         <v>0</v>
       </c>
@@ -6969,8 +7164,11 @@
       <c r="AG81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7202,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7036,8 +7235,8 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>4</v>
@@ -7054,8 +7253,8 @@
       <c r="R83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -7099,8 +7298,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,8 +7788,11 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7583,35 +7800,35 @@
         <v>-100</v>
       </c>
       <c r="E89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F89" s="3">
         <v>0</v>
       </c>
       <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
       <c r="I89" s="3">
         <v>0</v>
       </c>
       <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>500</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
       <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
         <v>-100</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
       <c r="O89" s="3">
         <v>0</v>
       </c>
@@ -7669,8 +7886,11 @@
       <c r="AG89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,8 +7924,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7799,8 +8020,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,8 +8216,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8010,19 +8240,19 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>600</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>4</v>
@@ -8039,8 +8269,8 @@
       <c r="R94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -8084,8 +8314,11 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8352,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,8 +8742,11 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8520,23 +8766,23 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3">
         <v>100</v>
       </c>
       <c r="K100" s="3">
+        <v>100</v>
+      </c>
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
@@ -8544,25 +8790,25 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>4</v>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
+      <c r="W100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X100" s="3">
         <v>0</v>
@@ -8594,8 +8840,11 @@
       <c r="AG100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8689,8 +8938,11 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8698,17 +8950,17 @@
         <v>-100</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
@@ -8716,11 +8968,11 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>500</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
@@ -8782,6 +9034,9 @@
         <v>0</v>
       </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PGID_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PGID_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
   <si>
     <t>PGID</t>
   </si>
@@ -656,148 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43951</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43769</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -832,28 +835,28 @@
         <v>0</v>
       </c>
       <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>100</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R8" s="3">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3">
         <v>400</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
@@ -894,8 +897,11 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -929,8 +935,8 @@
       <c r="M9" s="3">
         <v>0</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>4</v>
+      <c r="N9" s="3">
+        <v>0</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>4</v>
@@ -992,8 +998,11 @@
       <c r="AH9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1027,8 +1036,8 @@
       <c r="M10" s="3">
         <v>0</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>4</v>
+      <c r="N10" s="3">
+        <v>0</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>4</v>
@@ -1090,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1126,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1224,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,13 +1338,16 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1337,19 +1356,19 @@
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
@@ -1357,12 +1376,12 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1378,8 +1397,8 @@
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1420,16 +1439,19 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>4</v>
+      <c r="E15" s="3">
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>4</v>
@@ -1438,13 +1460,13 @@
         <v>4</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1455,8 +1477,8 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>4</v>
+      <c r="N15" s="3">
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>4</v>
@@ -1476,8 +1498,8 @@
       <c r="T15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1518,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,34 +1576,35 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F17" s="3">
         <v>100</v>
       </c>
       <c r="G17" s="3">
+        <v>100</v>
+      </c>
+      <c r="H17" s="3">
         <v>200</v>
       </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
       <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
         <v>100</v>
       </c>
-      <c r="J17" s="3">
-        <v>0</v>
-      </c>
       <c r="K17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L17" s="3">
         <v>100</v>
@@ -1587,11 +1613,11 @@
         <v>100</v>
       </c>
       <c r="N17" s="3">
+        <v>100</v>
+      </c>
+      <c r="O17" s="3">
         <v>200</v>
       </c>
-      <c r="O17" s="3">
-        <v>0</v>
-      </c>
       <c r="P17" s="3">
         <v>0</v>
       </c>
@@ -1599,11 +1625,11 @@
         <v>0</v>
       </c>
       <c r="R17" s="3">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3">
         <v>900</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
       <c r="T17" s="3">
         <v>0</v>
       </c>
@@ -1649,8 +1675,11 @@
       <c r="AH17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1658,25 +1687,25 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3">
         <v>-100</v>
       </c>
       <c r="G18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
       <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
         <v>-100</v>
       </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
       <c r="K18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3">
         <v>-100</v>
@@ -1687,8 +1716,8 @@
       <c r="N18" s="3">
         <v>-100</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
+      <c r="O18" s="3">
+        <v>-100</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>4</v>
@@ -1696,17 +1725,17 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3">
         <v>-500</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
+      <c r="U18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V18" s="3">
         <v>0</v>
@@ -1747,8 +1776,11 @@
       <c r="AH18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1816,13 +1849,13 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>4</v>
@@ -1830,17 +1863,17 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
+      <c r="U20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
@@ -1881,8 +1914,11 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1890,35 +1926,35 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>-100</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
       <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <v>-200</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
       <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>-100</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
       <c r="K21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3">
         <v>-100</v>
       </c>
       <c r="M21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N21" s="3">
         <v>200</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1979,8 +2015,11 @@
       <c r="AH21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2041,14 +2080,14 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>4</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -2077,47 +2116,50 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>-100</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
       <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>-200</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>-100</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
       <c r="K23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L23" s="3">
         <v>-100</v>
       </c>
       <c r="M23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N23" s="3">
         <v>100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-100</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
       <c r="P23" s="3">
         <v>0</v>
       </c>
@@ -2125,11 +2167,11 @@
         <v>0</v>
       </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>-800</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
         <v>0</v>
       </c>
@@ -2175,8 +2217,11 @@
       <c r="AH23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2273,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,47 +2419,50 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>-100</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
       <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>-200</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
       <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
       <c r="K26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L26" s="3">
         <v>-100</v>
       </c>
       <c r="M26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N26" s="3">
         <v>100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-100</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
       <c r="P26" s="3">
         <v>0</v>
       </c>
@@ -2419,11 +2470,11 @@
         <v>0</v>
       </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>-800</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
         <v>0</v>
       </c>
@@ -2469,47 +2520,50 @@
       <c r="AH26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>-100</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
       <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>-200</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
       <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
       <c r="K27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3">
         <v>-100</v>
       </c>
       <c r="M27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N27" s="3">
         <v>100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-100</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
       <c r="P27" s="3">
         <v>0</v>
       </c>
@@ -2517,11 +2571,11 @@
         <v>0</v>
       </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>-800</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
         <v>0</v>
       </c>
@@ -2567,8 +2621,11 @@
       <c r="AH27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2763,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2992,13 +3061,13 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>4</v>
@@ -3006,17 +3075,17 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
+      <c r="U32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V32" s="3">
         <v>0</v>
@@ -3057,47 +3126,50 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>-100</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
       <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>-200</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
       <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
       <c r="K33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3">
         <v>-100</v>
       </c>
       <c r="M33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N33" s="3">
         <v>100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-100</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
       <c r="P33" s="3">
         <v>0</v>
       </c>
@@ -3105,11 +3177,11 @@
         <v>0</v>
       </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-800</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
         <v>0</v>
       </c>
@@ -3155,8 +3227,11 @@
       <c r="AH33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,47 +3328,50 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>-100</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
       <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>-200</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
       <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
       <c r="K35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3">
         <v>-100</v>
       </c>
       <c r="M35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N35" s="3">
         <v>100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-100</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
       <c r="P35" s="3">
         <v>0</v>
       </c>
@@ -3301,11 +3379,11 @@
         <v>0</v>
       </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-800</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
         <v>0</v>
       </c>
@@ -3351,111 +3429,117 @@
       <c r="AH35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43951</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43769</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,8 +3611,9 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3535,7 +3621,7 @@
         <v>300</v>
       </c>
       <c r="E41" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F41" s="3">
         <v>400</v>
@@ -3544,29 +3630,29 @@
         <v>400</v>
       </c>
       <c r="H41" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I41" s="3">
         <v>500</v>
       </c>
       <c r="J41" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K41" s="3">
         <v>600</v>
       </c>
       <c r="L41" s="3">
+        <v>600</v>
+      </c>
+      <c r="M41" s="3">
         <v>500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>100</v>
       </c>
-      <c r="O41" s="3">
-        <v>0</v>
-      </c>
       <c r="P41" s="3">
         <v>0</v>
       </c>
@@ -3603,11 +3689,11 @@
       <c r="AA41" s="3">
         <v>0</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC41" s="3">
-        <v>0</v>
+      <c r="AB41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD41" s="3">
         <v>0</v>
@@ -3624,8 +3710,11 @@
       <c r="AH41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3722,8 +3811,11 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3760,8 +3852,8 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
+      <c r="O43" s="3">
+        <v>0</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>4</v>
@@ -3778,8 +3870,8 @@
       <c r="T43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -3820,8 +3912,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3838,13 +3933,13 @@
         <v>600</v>
       </c>
       <c r="H44" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="I44" s="3">
         <v>700</v>
       </c>
       <c r="J44" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="K44" s="3">
         <v>800</v>
@@ -3858,8 +3953,8 @@
       <c r="N44" s="3">
         <v>800</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
+      <c r="O44" s="3">
+        <v>800</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>4</v>
@@ -3876,8 +3971,8 @@
       <c r="T44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="U44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
@@ -3918,8 +4013,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3956,8 +4054,8 @@
       <c r="N45" s="3">
         <v>0</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>4</v>
+      <c r="O45" s="3">
+        <v>0</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>4</v>
@@ -3974,8 +4072,8 @@
       <c r="T45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U45" s="3">
-        <v>0</v>
+      <c r="U45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V45" s="3">
         <v>0</v>
@@ -3992,14 +4090,14 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC45" s="3" t="s">
-        <v>4</v>
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC45" s="3">
+        <v>0</v>
       </c>
       <c r="AD45" s="3" t="s">
         <v>4</v>
@@ -4016,8 +4114,11 @@
       <c r="AH45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4025,38 +4126,38 @@
         <v>900</v>
       </c>
       <c r="E46" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="F46" s="3">
         <v>1000</v>
       </c>
       <c r="G46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H46" s="3">
         <v>1100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1300</v>
-      </c>
-      <c r="J46" s="3">
-        <v>1400</v>
       </c>
       <c r="K46" s="3">
         <v>1400</v>
       </c>
       <c r="L46" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M46" s="3">
         <v>1300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>900</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4114,8 +4215,11 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4212,8 +4316,11 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4248,11 +4355,11 @@
         <v>0</v>
       </c>
       <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3">
         <v>500</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4268,8 +4375,8 @@
       <c r="T48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -4310,8 +4417,11 @@
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4343,13 +4453,13 @@
         <v>300</v>
       </c>
       <c r="M49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N49" s="3">
         <v>200</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
+      <c r="O49" s="3">
+        <v>200</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>4</v>
@@ -4366,8 +4476,8 @@
       <c r="T49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -4408,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4627,11 +4746,11 @@
       <c r="I52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>4</v>
@@ -4654,8 +4773,8 @@
       <c r="R52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
@@ -4702,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,47 +4922,50 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="E54" s="3">
         <v>1200</v>
       </c>
       <c r="F54" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="G54" s="3">
         <v>1300</v>
       </c>
       <c r="H54" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I54" s="3">
         <v>1500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1600</v>
-      </c>
-      <c r="J54" s="3">
-        <v>1700</v>
       </c>
       <c r="K54" s="3">
         <v>1700</v>
       </c>
       <c r="L54" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M54" s="3">
         <v>1600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1700</v>
       </c>
-      <c r="O54" s="3">
-        <v>0</v>
-      </c>
       <c r="P54" s="3">
         <v>0</v>
       </c>
@@ -4898,8 +5023,11 @@
       <c r="AH54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,8 +5099,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5008,8 +5138,8 @@
       <c r="N57" s="3">
         <v>0</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
+      <c r="O57" s="3">
+        <v>0</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>4</v>
@@ -5026,8 +5156,8 @@
       <c r="T57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
+      <c r="U57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
@@ -5068,8 +5198,11 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5082,8 +5215,8 @@
       <c r="F58" s="3">
         <v>0</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
+      <c r="G58" s="3">
+        <v>0</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>4</v>
@@ -5091,8 +5224,8 @@
       <c r="I58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
+      <c r="J58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5101,7 +5234,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N58" s="3">
         <v>100</v>
@@ -5122,7 +5255,7 @@
         <v>100</v>
       </c>
       <c r="T58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -5152,13 +5285,13 @@
         <v>0</v>
       </c>
       <c r="AD58" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AE58" s="3">
         <v>400</v>
       </c>
       <c r="AF58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AG58" s="3">
         <v>300</v>
@@ -5166,8 +5299,11 @@
       <c r="AH58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5195,17 +5331,17 @@
       <c r="K59" s="3">
         <v>0</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
+      <c r="L59" s="3">
+        <v>0</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N59" s="3">
-        <v>0</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O59" s="3">
+        <v>0</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>4</v>
@@ -5213,8 +5349,8 @@
       <c r="Q59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
+      <c r="R59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S59" s="3">
         <v>0</v>
@@ -5250,7 +5386,7 @@
         <v>0</v>
       </c>
       <c r="AD59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE59" s="3">
         <v>100</v>
@@ -5264,8 +5400,11 @@
       <c r="AH59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5297,7 +5436,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N60" s="3">
         <v>100</v>
@@ -5318,7 +5457,7 @@
         <v>100</v>
       </c>
       <c r="T60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U60" s="3">
         <v>0</v>
@@ -5348,7 +5487,7 @@
         <v>0</v>
       </c>
       <c r="AD60" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AE60" s="3">
         <v>400</v>
@@ -5362,8 +5501,11 @@
       <c r="AH60" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5392,7 +5534,7 @@
         <v>100</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -5460,25 +5602,28 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I62" s="3">
         <v>0</v>
@@ -5489,17 +5634,17 @@
       <c r="K62" s="3">
         <v>0</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
+      <c r="O62" s="3">
+        <v>0</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>4</v>
@@ -5516,8 +5661,8 @@
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
+      <c r="U62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V62" s="3">
         <v>0</v>
@@ -5558,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,8 +6006,11 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5873,7 +6030,7 @@
         <v>100</v>
       </c>
       <c r="I66" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J66" s="3">
         <v>200</v>
@@ -5882,10 +6039,10 @@
         <v>200</v>
       </c>
       <c r="L66" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N66" s="3">
         <v>100</v>
@@ -5906,7 +6063,7 @@
         <v>100</v>
       </c>
       <c r="T66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U66" s="3">
         <v>0</v>
@@ -5936,7 +6093,7 @@
         <v>0</v>
       </c>
       <c r="AD66" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AE66" s="3">
         <v>400</v>
@@ -5950,8 +6107,11 @@
       <c r="AH66" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6280,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,46 +6548,49 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-4900</v>
+        <v>-5000</v>
       </c>
       <c r="E72" s="3">
         <v>-4900</v>
       </c>
       <c r="F72" s="3">
-        <v>-4800</v>
+        <v>-4900</v>
       </c>
       <c r="G72" s="3">
         <v>-4800</v>
       </c>
       <c r="H72" s="3">
-        <v>-4600</v>
+        <v>-4800</v>
       </c>
       <c r="I72" s="3">
         <v>-4600</v>
       </c>
       <c r="J72" s="3">
-        <v>-4400</v>
+        <v>-4600</v>
       </c>
       <c r="K72" s="3">
         <v>-4400</v>
       </c>
       <c r="L72" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="M72" s="3">
         <v>-4300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-4200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-4300</v>
-      </c>
-      <c r="O72" s="3">
-        <v>-700</v>
       </c>
       <c r="P72" s="3">
         <v>-700</v>
@@ -6432,7 +6605,7 @@
         <v>-700</v>
       </c>
       <c r="T72" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="U72" s="3">
         <v>-600</v>
@@ -6476,8 +6649,11 @@
       <c r="AH72" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,46 +6952,49 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E76" s="3">
         <v>1100</v>
       </c>
       <c r="F76" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="G76" s="3">
         <v>1200</v>
       </c>
       <c r="H76" s="3">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="I76" s="3">
         <v>1400</v>
       </c>
       <c r="J76" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="K76" s="3">
         <v>1500</v>
       </c>
       <c r="L76" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M76" s="3">
         <v>1600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1600</v>
-      </c>
-      <c r="O76" s="3">
-        <v>-100</v>
       </c>
       <c r="P76" s="3">
         <v>-100</v>
@@ -6821,7 +7006,7 @@
         <v>-100</v>
       </c>
       <c r="S76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T76" s="3">
         <v>0</v>
@@ -6854,7 +7039,7 @@
         <v>0</v>
       </c>
       <c r="AD76" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="AE76" s="3">
         <v>-400</v>
@@ -6868,8 +7053,11 @@
       <c r="AH76" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,150 +7154,156 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43951</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43769</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>-100</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
       <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>-200</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
       <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
       <c r="K81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L81" s="3">
         <v>-100</v>
       </c>
       <c r="M81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N81" s="3">
         <v>100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-100</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
       <c r="P81" s="3">
         <v>0</v>
       </c>
@@ -7117,11 +7311,11 @@
         <v>0</v>
       </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-800</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
         <v>0</v>
       </c>
@@ -7167,8 +7361,11 @@
       <c r="AH81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7238,8 +7436,8 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>4</v>
@@ -7256,8 +7454,8 @@
       <c r="S83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -7301,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,47 +8004,50 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E89" s="3">
         <v>-100</v>
       </c>
       <c r="F89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
         <v>0</v>
       </c>
       <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>500</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
       <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
         <v>-100</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
       <c r="P89" s="3">
         <v>0</v>
       </c>
@@ -7889,8 +8105,11 @@
       <c r="AH89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8023,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,8 +8445,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8243,19 +8472,19 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>600</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>4</v>
@@ -8272,8 +8501,8 @@
       <c r="S94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -8317,8 +8546,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8451,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,8 +8987,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8769,23 +9014,23 @@
         <v>0</v>
       </c>
       <c r="J100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K100" s="3">
         <v>100</v>
       </c>
       <c r="L100" s="3">
+        <v>100</v>
+      </c>
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
@@ -8793,25 +9038,25 @@
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>4</v>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
+      <c r="X100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y100" s="3">
         <v>0</v>
@@ -8843,8 +9088,11 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8941,29 +9189,32 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
         <v>-100</v>
       </c>
       <c r="F102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
@@ -8971,11 +9222,11 @@
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>500</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
@@ -9037,6 +9288,9 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>
